--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488007_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488007_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>R. SANCHES CARDOSO MENDES</t>
+          <t>B. GARCIA ALVAREZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>11.9268</v>
+        <v>8.781700000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>10.8701</v>
+        <v>3.9739</v>
       </c>
       <c r="F2" t="n">
-        <v>1.0567</v>
+        <v>4.8078</v>
       </c>
       <c r="G2" t="n">
-        <v>1.6804</v>
+        <v>3.757</v>
       </c>
       <c r="H2" t="n">
-        <v>3.85</v>
+        <v>1.0477</v>
       </c>
       <c r="I2" t="n">
-        <v>-2.1696</v>
+        <v>2.7093</v>
       </c>
       <c r="J2" t="n">
-        <v>3.6718</v>
+        <v>4.1217</v>
       </c>
       <c r="K2" t="n">
-        <v>4.1099</v>
+        <v>2.3746</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.4381</v>
+        <v>1.7471</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.9914</v>
+        <v>-0.3647</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.2599</v>
+        <v>-1.3269</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.7315</v>
+        <v>0.9622000000000001</v>
       </c>
       <c r="P2" t="n">
-        <v>3.3698</v>
+        <v>2.9733</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="R2" t="n">
-        <v>3.3698</v>
+        <v>3.9645</v>
       </c>
       <c r="S2" t="n">
-        <v>5.936</v>
+        <v>0.4369</v>
       </c>
       <c r="T2" t="n">
-        <v>5.9912</v>
+        <v>0.2398</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0552</v>
+        <v>0.1971</v>
       </c>
       <c r="V2" t="n">
-        <v>0.9405</v>
+        <v>1.6145</v>
       </c>
       <c r="W2" t="n">
-        <v>1.2071</v>
+        <v>0.6036</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.2666</v>
+        <v>1.0109</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>B. GARCIA ALVAREZ</t>
+          <t>R. SANCHES CARDOSO MENDES</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>7.683</v>
+        <v>8.3613</v>
       </c>
       <c r="E3" t="n">
-        <v>2.7909</v>
+        <v>7.3047</v>
       </c>
       <c r="F3" t="n">
-        <v>4.8921</v>
+        <v>1.0567</v>
       </c>
       <c r="G3" t="n">
-        <v>3.757</v>
+        <v>1.6804</v>
       </c>
       <c r="H3" t="n">
-        <v>1.0477</v>
+        <v>3.85</v>
       </c>
       <c r="I3" t="n">
-        <v>2.7093</v>
+        <v>-2.1696</v>
       </c>
       <c r="J3" t="n">
-        <v>4.1217</v>
+        <v>3.6718</v>
       </c>
       <c r="K3" t="n">
-        <v>2.3746</v>
+        <v>4.1099</v>
       </c>
       <c r="L3" t="n">
-        <v>1.7471</v>
+        <v>-0.4381</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.3647</v>
+        <v>-1.9914</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.3269</v>
+        <v>-0.2599</v>
       </c>
       <c r="O3" t="n">
-        <v>0.9622000000000001</v>
+        <v>-1.7315</v>
       </c>
       <c r="P3" t="n">
-        <v>2.9733</v>
+        <v>3.3698</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>3.9645</v>
+        <v>3.3698</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.6619</v>
+        <v>2.3706</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.9432</v>
+        <v>2.4257</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2813</v>
+        <v>-0.0552</v>
       </c>
       <c r="V3" t="n">
-        <v>1.6145</v>
+        <v>0.9405</v>
       </c>
       <c r="W3" t="n">
-        <v>0.6036</v>
+        <v>1.2071</v>
       </c>
       <c r="X3" t="n">
-        <v>1.0109</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.0409</v>
+        <v>3.673</v>
       </c>
       <c r="E4" t="n">
-        <v>1.8742</v>
+        <v>2.2817</v>
       </c>
       <c r="F4" t="n">
-        <v>1.1667</v>
+        <v>1.3913</v>
       </c>
       <c r="G4" t="n">
         <v>-0.4773</v>
@@ -766,13 +766,13 @@
         <v>3.1716</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2783</v>
+        <v>0.9104</v>
       </c>
       <c r="T4" t="n">
-        <v>0.4957</v>
+        <v>0.9032</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2174</v>
+        <v>0.0072</v>
       </c>
       <c r="V4" t="n">
         <v>0.2666</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.9492</v>
+        <v>3.0935</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3324</v>
+        <v>0.8418</v>
       </c>
       <c r="F5" t="n">
-        <v>2.6167</v>
+        <v>2.2517</v>
       </c>
       <c r="G5" t="n">
         <v>0.9747</v>
@@ -844,13 +844,13 @@
         <v>1.5858</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.3537</v>
+        <v>-0.2093</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.9360000000000001</v>
+        <v>-0.4266</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5823</v>
+        <v>0.2173</v>
       </c>
       <c r="V5" t="n">
         <v>0.9405</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.779</v>
+        <v>2.9133</v>
       </c>
       <c r="E6" t="n">
-        <v>1.3344</v>
+        <v>2.0475</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4446</v>
+        <v>0.8658</v>
       </c>
       <c r="G6" t="n">
         <v>1.6039</v>
@@ -922,13 +922,13 @@
         <v>2.3787</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.6772</v>
+        <v>0.457</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1834</v>
+        <v>0.5296999999999999</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4938</v>
+        <v>-0.0727</v>
       </c>
       <c r="V6" t="n">
         <v>-0.337</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2719</v>
+        <v>1.5919</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.6521</v>
+        <v>0.0609</v>
       </c>
       <c r="F7" t="n">
-        <v>1.9241</v>
+        <v>1.531</v>
       </c>
       <c r="G7" t="n">
         <v>1.2405</v>
@@ -1000,13 +1000,13 @@
         <v>2.5769</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2769</v>
+        <v>0.0431</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.9360000000000001</v>
+        <v>-0.2229</v>
       </c>
       <c r="U7" t="n">
-        <v>0.6591</v>
+        <v>0.266</v>
       </c>
       <c r="V7" t="n">
         <v>-1.2775</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>I. RODRIGUEZ SOLER</t>
+          <t>M. HETOR MENSAH</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5692</v>
+        <v>0.337</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0619</v>
+        <v>0.3208</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5073</v>
+        <v>0.0162</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.7017</v>
+        <v>1.3772</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5207000000000001</v>
+        <v>3.5582</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.2224</v>
+        <v>-2.181</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.1092</v>
+        <v>3.3023</v>
       </c>
       <c r="K8" t="n">
-        <v>0.249</v>
+        <v>4.4195</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.3583</v>
+        <v>-1.1172</v>
       </c>
       <c r="M8" t="n">
-        <v>0.4075</v>
+        <v>-1.9251</v>
       </c>
       <c r="N8" t="n">
-        <v>0.2717</v>
+        <v>-0.8613</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1358</v>
+        <v>-1.0638</v>
       </c>
       <c r="P8" t="n">
-        <v>0.1982</v>
+        <v>-0.3964</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-3.9645</v>
       </c>
       <c r="R8" t="n">
-        <v>0.1982</v>
+        <v>3.568</v>
       </c>
       <c r="S8" t="n">
-        <v>1.0727</v>
+        <v>0.9004</v>
       </c>
       <c r="T8" t="n">
-        <v>1.1711</v>
+        <v>0.4499</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0984</v>
+        <v>0.4505</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-1.5441</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.5331</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-2.0772</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. HETOR MENSAH</t>
+          <t>I. RODRIGUEZ SOLER</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.0071</v>
+        <v>0.0765</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1171</v>
+        <v>-0.487</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.1242</v>
+        <v>0.5635</v>
       </c>
       <c r="G9" t="n">
-        <v>1.3772</v>
+        <v>-0.7017</v>
       </c>
       <c r="H9" t="n">
-        <v>3.5582</v>
+        <v>0.5207000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.181</v>
+        <v>-1.2224</v>
       </c>
       <c r="J9" t="n">
-        <v>3.3023</v>
+        <v>-1.1092</v>
       </c>
       <c r="K9" t="n">
-        <v>4.4195</v>
+        <v>0.249</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.1172</v>
+        <v>-1.3583</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.9251</v>
+        <v>0.4075</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.8613</v>
+        <v>0.2717</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.0638</v>
+        <v>0.1358</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.3964</v>
+        <v>0.1982</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.9645</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>3.568</v>
+        <v>0.1982</v>
       </c>
       <c r="S9" t="n">
-        <v>0.5562</v>
+        <v>0.58</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2461</v>
+        <v>0.6222</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3101</v>
+        <v>-0.0422</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.5441</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5331</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.0772</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.5812</v>
+        <v>-0.3359</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.5253</v>
+        <v>-1.0554</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9441000000000001</v>
+        <v>0.7195</v>
       </c>
       <c r="G10" t="n">
         <v>-0.9306</v>
@@ -1234,13 +1234,13 @@
         <v>0.1982</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1512</v>
+        <v>0.3964</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1872</v>
+        <v>0.2827</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3384</v>
+        <v>0.1138</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.2458</v>
+        <v>-0.3933</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.1222</v>
+        <v>-1.5504</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8763</v>
+        <v>1.1571</v>
       </c>
       <c r="G11" t="n">
         <v>-0.4631</v>
@@ -1312,13 +1312,13 @@
         <v>1.784</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8443000000000001</v>
+        <v>0.0083</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.433</v>
+        <v>0.1388</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4113</v>
+        <v>-0.1305</v>
       </c>
       <c r="V11" t="n">
         <v>-0.5331</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.9635</v>
+        <v>-3.3648</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.3901</v>
+        <v>-3.7352</v>
       </c>
       <c r="F12" t="n">
-        <v>0.4266</v>
+        <v>0.3704</v>
       </c>
       <c r="G12" t="n">
         <v>-0.4622</v>
@@ -1390,13 +1390,13 @@
         <v>0.9911</v>
       </c>
       <c r="S12" t="n">
-        <v>0.6196</v>
+        <v>0.2184</v>
       </c>
       <c r="T12" t="n">
-        <v>0.6719000000000001</v>
+        <v>0.3268</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0523</v>
+        <v>-0.1084</v>
       </c>
       <c r="V12" t="n">
         <v>-0.9405</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>24.4224</v>
+        <v>24.7342</v>
       </c>
       <c r="E13" t="n">
-        <v>9.691300000000004</v>
+        <v>10.0033</v>
       </c>
       <c r="F13" t="n">
         <v>14.731</v>
@@ -1468,13 +1468,13 @@
         <v>23.7868</v>
       </c>
       <c r="S13" t="n">
-        <v>5.800000000000001</v>
+        <v>6.1122</v>
       </c>
       <c r="T13" t="n">
-        <v>4.9572</v>
+        <v>5.269299999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>0.8428</v>
+        <v>0.8428999999999998</v>
       </c>
       <c r="V13" t="n">
         <v>-0.8700999999999997</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.9466</v>
+        <v>3.4002</v>
       </c>
       <c r="E14" t="n">
-        <v>5.3977</v>
+        <v>4.2772</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.4512</v>
+        <v>-0.8769</v>
       </c>
       <c r="G14" t="n">
         <v>4.6201</v>
@@ -1546,13 +1546,13 @@
         <v>1.9822</v>
       </c>
       <c r="S14" t="n">
-        <v>1.7509</v>
+        <v>0.2046</v>
       </c>
       <c r="T14" t="n">
-        <v>1.3548</v>
+        <v>0.2342</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3961</v>
+        <v>-0.0296</v>
       </c>
       <c r="V14" t="n">
         <v>2.54</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5214</v>
+        <v>0.7637</v>
       </c>
       <c r="E15" t="n">
-        <v>1.3647</v>
+        <v>1.4666</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.8433</v>
+        <v>-0.7029</v>
       </c>
       <c r="G15" t="n">
         <v>0.7398</v>
@@ -1624,13 +1624,13 @@
         <v>0.3964</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.6148</v>
+        <v>-0.3726</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.4368</v>
+        <v>-0.3349</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1781</v>
+        <v>-0.0377</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3424</v>
+        <v>0.5004999999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.0202</v>
+        <v>0.08169999999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3626</v>
+        <v>0.4188</v>
       </c>
       <c r="G16" t="n">
         <v>0.2316</v>
@@ -1702,13 +1702,13 @@
         <v>0.5947</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.4838</v>
+        <v>-0.3258</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.0403</v>
+        <v>0.0615</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4435</v>
+        <v>-0.3873</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.6083</v>
+        <v>-0.6926</v>
       </c>
       <c r="E18" t="n">
         <v>-0.5947</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.0137</v>
+        <v>-0.0979</v>
       </c>
       <c r="G18" t="n">
         <v>-0.4677</v>
@@ -1858,13 +1858,13 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1406</v>
+        <v>-0.2249</v>
       </c>
       <c r="T18" t="n">
         <v>0.08450000000000001</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2251</v>
+        <v>-0.3093</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.1175</v>
+        <v>-1.4617</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.9288</v>
+        <v>-1.1325</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.1888</v>
+        <v>-0.3292</v>
       </c>
       <c r="G19" t="n">
         <v>0.0665</v>
@@ -1936,13 +1936,13 @@
         <v>0.9911</v>
       </c>
       <c r="S19" t="n">
-        <v>0.6772</v>
+        <v>0.3331</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2975</v>
+        <v>0.09379999999999999</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3797</v>
+        <v>0.2393</v>
       </c>
       <c r="V19" t="n">
         <v>-0.8701</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>B. GIMENEZ SALAZAR</t>
+          <t>S. MAILLO CABRERIZO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.5479</v>
+        <v>-1.4781</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.6682</v>
+        <v>-0.9004</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.8796</v>
+        <v>-0.5777</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.2257</v>
+        <v>-0.0144</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.7402</v>
+        <v>-0.066</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5145</v>
+        <v>0.0516</v>
       </c>
       <c r="J20" t="n">
-        <v>0.8844</v>
+        <v>0.0402</v>
       </c>
       <c r="K20" t="n">
-        <v>0.1211</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0.7634</v>
+        <v>0.0402</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.1101</v>
+        <v>-0.0545</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.8613</v>
+        <v>-0.066</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.2488</v>
+        <v>0.0114</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.5947</v>
+        <v>-0.9911</v>
       </c>
       <c r="Q20" t="n">
         <v>-0.9911</v>
       </c>
       <c r="R20" t="n">
-        <v>0.3964</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0.1426</v>
+        <v>-0.4726</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5616</v>
+        <v>0.0505</v>
       </c>
       <c r="U20" t="n">
-        <v>0.7042</v>
+        <v>-0.5231</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.8701</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.8701</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S. MAILLO CABRERIZO</t>
+          <t>B. GIMENEZ SALAZAR</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.6361</v>
+        <v>-1.9338</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.0023</v>
+        <v>-0.4645</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.6338</v>
+        <v>-1.4693</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.0144</v>
+        <v>-0.2257</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.066</v>
+        <v>-0.7402</v>
       </c>
       <c r="I21" t="n">
-        <v>0.0516</v>
+        <v>0.5145</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0402</v>
+        <v>0.8844</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>0.1211</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0402</v>
+        <v>0.7634</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.0545</v>
+        <v>-1.1101</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.066</v>
+        <v>-0.8613</v>
       </c>
       <c r="O21" t="n">
-        <v>0.0114</v>
+        <v>-0.2488</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.9911</v>
+        <v>-0.5947</v>
       </c>
       <c r="Q21" t="n">
         <v>-0.9911</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>0.3964</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6307</v>
+        <v>-0.2433</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.0514</v>
+        <v>-0.3578</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5793</v>
+        <v>0.1145</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-0.8701</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.8701</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.9374</v>
+        <v>-2.9211</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.4433</v>
+        <v>-2.647</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.4941</v>
+        <v>-0.2741</v>
       </c>
       <c r="G22" t="n">
         <v>-0.8915999999999999</v>
@@ -2170,13 +2170,13 @@
         <v>0.7929</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5899</v>
+        <v>-0.5736</v>
       </c>
       <c r="T22" t="n">
-        <v>0.514</v>
+        <v>0.3103</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.1039</v>
+        <v>-0.8838</v>
       </c>
       <c r="V22" t="n">
         <v>-0.2666</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.1857</v>
+        <v>-4.0558</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.113</v>
+        <v>-3.0111</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.0728</v>
+        <v>-1.0447</v>
       </c>
       <c r="G23" t="n">
         <v>-5.5457</v>
@@ -2248,13 +2248,13 @@
         <v>1.784</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.1574</v>
+        <v>-0.0275</v>
       </c>
       <c r="T23" t="n">
-        <v>0.0076</v>
+        <v>0.1095</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.165</v>
+        <v>-0.1369</v>
       </c>
       <c r="V23" t="n">
         <v>-0.2666</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.4236</v>
+        <v>-4.6629</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.113</v>
+        <v>-2.9092</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.3107</v>
+        <v>-1.7537</v>
       </c>
       <c r="G24" t="n">
         <v>-1.9274</v>
@@ -2326,13 +2326,13 @@
         <v>1.9822</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.6794</v>
+        <v>-0.9186</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.8184</v>
+        <v>-0.6147</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.861</v>
+        <v>-0.304</v>
       </c>
       <c r="V24" t="n">
         <v>2.1476</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-6.0815</v>
+        <v>-4.8572</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.3137</v>
+        <v>-2.7025</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.7678</v>
+        <v>-2.1546</v>
       </c>
       <c r="G25" t="n">
         <v>-3.6357</v>
@@ -2404,13 +2404,13 @@
         <v>1.3876</v>
       </c>
       <c r="S25" t="n">
-        <v>-2.8423</v>
+        <v>-1.6179</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.1232</v>
+        <v>-0.5119</v>
       </c>
       <c r="U25" t="n">
-        <v>-1.7192</v>
+        <v>-1.106</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-6.9971</v>
+        <v>-6.647</v>
       </c>
       <c r="E26" t="n">
-        <v>-5.3917</v>
+        <v>-5.2899</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.6053</v>
+        <v>-1.3572</v>
       </c>
       <c r="G26" t="n">
         <v>-0.8512</v>
@@ -2482,13 +2482,13 @@
         <v>1.5858</v>
       </c>
       <c r="S26" t="n">
-        <v>-1.232</v>
+        <v>-0.882</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.0696</v>
+        <v>0.0322</v>
       </c>
       <c r="U26" t="n">
-        <v>-1.1624</v>
+        <v>-0.9142</v>
       </c>
       <c r="V26" t="n">
         <v>-1.5441</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-24.422</v>
+        <v>-23.7431</v>
       </c>
       <c r="E27" t="n">
-        <v>-13.5238</v>
+        <v>-13.5236</v>
       </c>
       <c r="F27" t="n">
-        <v>-10.8985</v>
+        <v>-10.2194</v>
       </c>
       <c r="G27" t="n">
         <v>-7.598700000000001</v>
@@ -2560,13 +2560,13 @@
         <v>11.8933</v>
       </c>
       <c r="S27" t="n">
-        <v>-5.8002</v>
+        <v>-5.121099999999999</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.8429000000000001</v>
+        <v>-0.8428</v>
       </c>
       <c r="U27" t="n">
-        <v>-4.9575</v>
+        <v>-4.2781</v>
       </c>
       <c r="V27" t="n">
         <v>0.8701000000000001</v>
